--- a/Event_剧情事件表.xlsx
+++ b/Event_剧情事件表.xlsx
@@ -158,7 +158,7 @@
     <t>村口的陌生人</t>
   </si>
   <si>
-    <t>一名风尘仆仆的旅人在村口打听消息。他说自己从很远的地方来。</t>
+    <t>一名风尘仆仆的旅人来到村口。他带来了补给和图纸，请你从中收下一份。</t>
   </si>
 </sst>
 </file>
